--- a/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GAB3H6</t>
+          <t>AB1005</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,24 +487,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3H6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1005</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ABP253</t>
+          <t>AB1006</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -514,24 +514,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
+          <t>Svenska: 10 mål, engelska: 1 mål (diff 9)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP253</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1006</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ABP254</t>
+          <t>AB1009</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -541,24 +541,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP254</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1009</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GBP32U</t>
+          <t>AB1011</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -568,24 +568,24 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1011</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GBP32V</t>
+          <t>AB1016</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -595,24 +595,24 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1016</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GBP32W</t>
+          <t>AB1019</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -622,24 +622,24 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+          <t>Svenska: 8 mål, engelska: 6 mål (diff 2)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AB1019</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GBP34H</t>
+          <t>GAB3H6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BIL</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP34H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAB3H6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GBP365</t>
+          <t>ABP253</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,24 +676,24 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP365</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP253</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ABQ2AZ</t>
+          <t>ABP254</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -703,24 +703,24 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABP254</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ABQ2B2</t>
+          <t>GBP32U</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -730,24 +730,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32U</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ABQ2B4</t>
+          <t>GBP32V</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BPO</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -757,24 +757,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32V</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>FI1028</t>
+          <t>GBP32W</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -784,24 +784,24 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP32W</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GFI37Z</t>
+          <t>GBP34H</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP34H</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GFI3BT</t>
+          <t>GBP365</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FIA</t>
+          <t>BIL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBP365</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GHI33T</t>
+          <t>ABQ2AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,24 +865,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+          <t>Svenska: 5 mål, engelska: 6 mål (diff 1)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AM</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GHI33V</t>
+          <t>ABQ2AZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -892,24 +892,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2AZ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GHI33W</t>
+          <t>ABQ2B2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -919,24 +919,24 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33W</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GHI35A</t>
+          <t>ABQ2B4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -946,24 +946,24 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ABQ2B4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GHI362</t>
+          <t>GBQ2HC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -973,24 +973,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2HC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GHI374</t>
+          <t>GBQ2UB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1000,24 +1000,24 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI374</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2UB</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GHI378</t>
+          <t>GBQ2WH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1027,24 +1027,24 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI378</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GBQ2WH</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GHI3JX</t>
+          <t>EU1027</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HIA</t>
+          <t>EUN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1054,24 +1054,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3JX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EU1027</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GNA3B8</t>
+          <t>FI1028</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 6 mål (diff 1)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1028</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>NA2001</t>
+          <t>FI1034</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 3 mål (diff 1)</t>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI1034</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>NA3001</t>
+          <t>FI2003</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1135,24 +1135,24 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 9 mål (diff 1)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FI2003</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>NA3005</t>
+          <t>GFI37Z</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1162,24 +1162,24 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 6 mål (diff 1)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI37Z</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>NA3007</t>
+          <t>GFI3BT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NAA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1189,24 +1189,24 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>APG244</t>
+          <t>GFI3BU</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,24 +1216,24 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFI3BU</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>APG245</t>
+          <t>GHI29Y</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1243,24 +1243,24 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI29Y</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>GHI2CN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>GHI2CP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,24 +1297,24 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CP</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>GHI2CQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CQ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>GHI2CR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1351,24 +1351,24 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 18 mål, engelska: 0 mål (diff 18)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI2CR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>APG2BC</t>
+          <t>GHI32G</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1378,24 +1378,24 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI32G</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>APG2C7</t>
+          <t>GHI33T</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1405,24 +1405,24 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33T</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GPG22J</t>
+          <t>GHI33V</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1432,24 +1432,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33V</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GPG2E7</t>
+          <t>GHI33W</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI33W</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>GHI35A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1486,24 +1486,24 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI35A</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>GHI362</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1513,24 +1513,24 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 14 mål (diff 1)</t>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI362</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>GHI374</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1540,24 +1540,24 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 14 mål (diff 1)</t>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI374</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>GHI378</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1567,24 +1567,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+          <t>Svenska: 14 mål, engelska: 0 mål (diff 14)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI378</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>GHI37M</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1594,24 +1594,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI37M</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>GHI3JX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1621,24 +1621,24 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GHI3JX</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>HI1004</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1648,24 +1648,24 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1004</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GPG2YG</t>
+          <t>HI1009</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1675,24 +1675,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1009</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>HI1011</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1702,24 +1702,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1011</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GPG326</t>
+          <t>HI1013</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1734,19 +1734,19 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1013</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GPG3AB</t>
+          <t>HI1014</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1014</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>HI1015</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>HIA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+          <t>Svenska: 18 mål, engelska: 0 mål (diff 18)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=HI1015</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>KG1005</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+          <t>Svenska: 0 mål, engelska: 7 mål (diff 7)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1005</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>KG1010</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1010</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>KG1020</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG1020</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>KG2001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Svenska: 27 mål, engelska: 0 mål (diff 27)</t>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2001</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>KG2005</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG2005</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>KG3016</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>KGA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KG3016</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GLP2FZ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GLP2FZ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>LP2009</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>LPU</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=LP2009</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>GNA2RY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA2RY</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>GNA3B7</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 6 mål (diff 1)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GNA3B8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 5 mål, engelska: 6 mål (diff 1)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNA3B8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>NA1027</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 10 mål, engelska: 11 mål (diff 1)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA1027</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>NA2001</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+          <t>Svenska: 4 mål, engelska: 3 mål (diff 1)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA2001</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>NA3001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 10 mål, engelska: 9 mål (diff 1)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3001</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>NA3005</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 7 mål, engelska: 6 mål (diff 1)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3005</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>NA3007</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>NAA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NA3007</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>PE1010</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 0 mål (diff 22)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1010</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GRK32C</t>
+          <t>PE1018</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1018</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>PE1023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1023</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>PE1039</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1039</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>PE1050</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 0 mål (diff 19)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1050</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>PE1052</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>PEA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,44 +2377,1988 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1052</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>PE1053</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Svenska: 2 mål, engelska: 0 mål (diff 2)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1053</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>PE1054</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1054</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>PE1055</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1055</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>PE1056</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1056</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>PE1057</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1057</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>PE1058</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE1058</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>PE2016</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>PE2017</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>PE3004</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>PE3012</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>PEA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PE3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>APG244</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>APG245</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>APG246</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>APG247</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>APG24E</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>APG27Z</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>APG28R</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>APG2BC</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Svenska: 12 mål, engelska: 0 mål (diff 12)</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>APG2BF</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>APG2C7</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>GPG22J</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>GPG2E7</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>GPG2LZ</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GPG2N7</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GPG2QP</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 14 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GPG2RH</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 14 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GPG2RR</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GPG2RS</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>GPG2S7</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>GPG2S8</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>GPG2SC</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Svenska: 27 mål, engelska: 0 mål (diff 27)</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>GPG2VW</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>GPG2YG</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>GPG2Z3</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>GPG326</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>GPG36A</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Svenska: 17 mål, engelska: 0 mål (diff 17)</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>GPG36B</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Svenska: 18 mål, engelska: 0 mål (diff 18)</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>GPG3AB</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GPG3AF</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CF</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CG</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CH</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CJ</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GPG3CL</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Svenska: 27 mål, engelska: 0 mål (diff 27)</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GPG3EU</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GPG3EV</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>GPG3FV</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>PG3024</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>PG3025</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>PG3041</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PGA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GRK2P3</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GRK2P4</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Svenska: 22 mål, engelska: 0 mål (diff 22)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>GRK2Q4</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GRK2Q5</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GRK2TW</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GRK2TY</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GRK2TZ</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>GRK324</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Svenska: 22 mål, engelska: 0 mål (diff 22)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>GRK32C</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>RKA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GRV3BF</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>RV1039</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>RVA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 4 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>SK2015</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>GSO2UA</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 0 mål (diff 16)</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XU</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Svenska: 19 mål, engelska: 0 mål (diff 19)</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XV</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>GSO33U</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 0 mål (diff 13)</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>SO1019</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
           <t>SO1030</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>SOA</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
         <is>
           <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>GTR2UM</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>TR1011</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Svenska: 0 mål, engelska: 7 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>TR1018</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>TR2004</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 0 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E73"/>
+  <autoFilter ref="A1:E145"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2560,6 +4504,150 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId288"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$145</definedName>

--- a/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$145</definedName>

--- a/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$613</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$644</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E613"/>
+  <dimension ref="A1:E644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10408,39 +10408,39 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>GPA2FL</t>
+          <t>FPA0001</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Lärandemål skrivet som löpande text (4 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0001</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>GPA2FW</t>
+          <t>FPA0002</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -10450,24 +10450,24 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0002</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>GPA2K3</t>
+          <t>FPA0003</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -10477,51 +10477,51 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 1 mål, engelska: 5 mål (diff 4)</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>GPA2KU</t>
+          <t>FPA0003</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0003</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>GPA2LM</t>
+          <t>FPA0004</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -10536,19 +10536,19 @@
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0004</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>GPA2LN</t>
+          <t>FPA0005</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -10563,19 +10563,19 @@
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0005</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>GPA2NY</t>
+          <t>FPA0006</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -10590,19 +10590,19 @@
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0006</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>GPA2P7</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -10612,105 +10612,105 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>GPA2R6</t>
+          <t>FPA0007</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA0007</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>GPA32D</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Lärandemål skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>GPA32E</t>
+          <t>FPA2226</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2226</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>GPA353</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10720,51 +10720,51 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>GPA354</t>
+          <t>FPA2227</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2227</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>GPA357</t>
+          <t>FPA2228</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10774,24 +10774,24 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA357</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA2228</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>PA2008</t>
+          <t>FPA222A</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10801,24 +10801,24 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222A</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>PA2009</t>
+          <t>FPA222B</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10828,51 +10828,51 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 2 mål, engelska: 0 mål (diff 2)</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>PA2010</t>
+          <t>FPA222B</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Lärandemål skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222B</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>PA2011</t>
+          <t>FPA222C</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PEE</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -10882,78 +10882,78 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>APG22X</t>
+          <t>FPA222C</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222C</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>APG244</t>
+          <t>FPA222D</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>APG244</t>
+          <t>FPA222D</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -10968,19 +10968,19 @@
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222D</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>APG245</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -10990,78 +10990,78 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>APG245</t>
+          <t>FPA222E</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222E</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>FPA222F</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>APG246</t>
+          <t>FPA222F</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11076,19 +11076,19 @@
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222F</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11098,51 +11098,51 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>APG247</t>
+          <t>FPA222G</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222G</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>APG24D</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11152,105 +11152,105 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>FPA222J</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Lärandemål skrivet som löpande text (3 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222J</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>APG24E</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 2 mål, engelska: 0 mål (diff 2)</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>APG24S</t>
+          <t>FPA222N</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEDAGARB</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Lärandemål skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FPA222N</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>APG25N</t>
+          <t>GPA2FL</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11265,19 +11265,19 @@
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FL</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>APG26D</t>
+          <t>GPA2FW</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -11287,24 +11287,24 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2FW</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>APG275</t>
+          <t>GPA2K3</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -11314,24 +11314,24 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2K3</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>APG276</t>
+          <t>GPA2KU</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -11341,24 +11341,24 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2KU</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>GPA2LM</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -11368,51 +11368,51 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 2 mål (diff 10)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LM</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>APG27Z</t>
+          <t>GPA2LN</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2LN</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>APG282</t>
+          <t>GPA2NY</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -11422,24 +11422,24 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2NY</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>APG28B</t>
+          <t>GPA2P7</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -11449,24 +11449,24 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2P7</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>APG28M</t>
+          <t>GPA2R6</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -11476,24 +11476,24 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA2R6</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>GPA32D</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -11503,51 +11503,51 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32D</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>APG28R</t>
+          <t>GPA32E</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA32E</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>APG28S</t>
+          <t>GPA353</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -11557,24 +11557,24 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA353</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>APG29G</t>
+          <t>GPA354</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -11584,24 +11584,24 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA354</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>APG2AJ</t>
+          <t>GPA357</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -11611,24 +11611,24 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPA357</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>APG2BC</t>
+          <t>PA2008</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -11638,51 +11638,51 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Svenska: 12 mål, engelska: 2 mål (diff 10)</t>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2008</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>APG2BC</t>
+          <t>PA2009</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2009</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>APG2BF</t>
+          <t>PA2010</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -11692,24 +11692,24 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2010</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>APG2BK</t>
+          <t>PA2011</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>PEE</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -11719,19 +11719,19 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PA2011</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>APG2C3</t>
+          <t>APG22X</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -11746,19 +11746,19 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG22X</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>APG2C6</t>
+          <t>APG244</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -11773,19 +11773,19 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>APG2C7</t>
+          <t>APG244</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -11795,24 +11795,24 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG244</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>APG2C7</t>
+          <t>APG245</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -11822,24 +11822,24 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>APG2CC</t>
+          <t>APG245</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -11849,24 +11849,24 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG245</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>APG2CD</t>
+          <t>APG246</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -11881,19 +11881,19 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>APG2CL</t>
+          <t>APG246</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -11903,24 +11903,24 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG246</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>APG2CM</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -11935,19 +11935,19 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>GPG22J</t>
+          <t>APG247</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -11957,24 +11957,24 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG247</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>GPG22J</t>
+          <t>APG24D</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -11984,24 +11984,24 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24D</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>GPG27X</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -12016,19 +12016,19 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>GPG2E6</t>
+          <t>APG24E</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -12038,24 +12038,24 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24E</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>GPG2E7</t>
+          <t>APG24S</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -12070,19 +12070,19 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG24S</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>GPG2E7</t>
+          <t>APG25N</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -12092,24 +12092,24 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG25N</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>APG26D</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -12124,19 +12124,19 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG26D</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>GPG2LZ</t>
+          <t>APG275</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -12146,24 +12146,24 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG275</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>APG276</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -12178,19 +12178,19 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG276</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>GPG2N7</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -12200,24 +12200,24 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 12 mål, engelska: 2 mål (diff 10)</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>GPG2QP</t>
+          <t>APG27Z</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -12227,24 +12227,24 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 14 mål (diff 1)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG27Z</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>GPG2RH</t>
+          <t>APG282</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -12259,19 +12259,19 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 14 mål (diff 1)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG282</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>GPG2RR</t>
+          <t>APG28B</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -12286,19 +12286,19 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28B</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>GPG2RS</t>
+          <t>APG28M</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -12313,19 +12313,19 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28M</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>GPG2S7</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -12340,19 +12340,19 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>GPG2S8</t>
+          <t>APG28R</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -12362,24 +12362,24 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28R</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>APG28S</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -12394,19 +12394,19 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG28S</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>APG29G</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -12416,24 +12416,24 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG29G</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>APG2AJ</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -12448,19 +12448,19 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+          <t>Svenska: 11 mål, engelska: 0 mål (diff 11)</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2AJ</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>APG2BC</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -12475,19 +12475,19 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 12 mål, engelska: 2 mål (diff 10)</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>GPG2YG</t>
+          <t>APG2BC</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -12497,24 +12497,24 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 3 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BC</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>GPG2YG</t>
+          <t>APG2BF</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -12524,24 +12524,24 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (3 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BF</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>APG2BK</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -12556,19 +12556,19 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2BK</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>APG2C3</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -12583,19 +12583,19 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C3</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>APG2C6</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -12605,24 +12605,24 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C6</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>APG2C7</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -12637,19 +12637,19 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>APG2C7</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -12659,24 +12659,24 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2C7</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z7</t>
+          <t>APG2CC</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -12691,19 +12691,19 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CC</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>GPG326</t>
+          <t>APG2CD</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -12718,19 +12718,19 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CD</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>GPG326</t>
+          <t>APG2CL</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -12740,24 +12740,24 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CL</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>GPG327</t>
+          <t>APG2CM</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -12772,19 +12772,19 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG327</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=APG2CM</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG22J</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -12799,19 +12799,19 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG22J</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -12821,24 +12821,24 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG22J</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>GPG32A</t>
+          <t>GPG27X</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -12853,19 +12853,19 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG32A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG27X</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>GPG33D</t>
+          <t>GPG2E6</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -12880,19 +12880,19 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E6</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>GPG33E</t>
+          <t>GPG2E7</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -12907,19 +12907,19 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>GPG2E7</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -12929,24 +12929,24 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2E7</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -12961,19 +12961,19 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Svenska: 17 mål, engelska: 2 mål (diff 15)</t>
+          <t>Svenska: 6 mål, engelska: 1 mål (diff 5)</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG2LZ</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -12988,19 +12988,19 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2LZ</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -13015,19 +13015,19 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Svenska: 18 mål, engelska: 2 mål (diff 16)</t>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG2N7</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -13042,19 +13042,19 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2N7</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>GPG3AB</t>
+          <t>GPG2QP</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -13064,24 +13064,24 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (5 mål utan punktlista)</t>
+          <t>Svenska: 15 mål, engelska: 14 mål (diff 1)</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2QP</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>GPG3AF</t>
+          <t>GPG2RH</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -13096,19 +13096,19 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Svenska: 15 mål, engelska: 14 mål (diff 1)</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RH</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>GPG3AF</t>
+          <t>GPG2RR</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -13118,24 +13118,24 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RR</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>GPG3BD</t>
+          <t>GPG2RS</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -13150,19 +13150,19 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2RS</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>GPG3BE</t>
+          <t>GPG2S7</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -13177,19 +13177,19 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S7</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG2S8</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -13204,19 +13204,19 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
+          <t>Svenska: 16 mål, engelska: 15 mål (diff 1)</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2S8</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -13226,24 +13226,24 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG2SC</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -13253,24 +13253,24 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -13280,24 +13280,24 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -13312,19 +13312,19 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG2YG</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -13334,24 +13334,24 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 8 mål, engelska: 3 mål (diff 5)</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG2YG</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -13361,24 +13361,24 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
+          <t>Learning Outcomes skrivet som löpande text (3 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -13388,24 +13388,24 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -13420,19 +13420,19 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -13442,24 +13442,24 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Svenska: 27 mål, engelska: 2 mål (diff 25)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -13469,24 +13469,24 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>GPG3CN</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -13501,19 +13501,19 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG2Z7</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -13528,19 +13528,19 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG326</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -13550,24 +13550,24 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GPG326</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -13577,24 +13577,24 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GPG327</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -13604,24 +13604,24 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG327</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -13636,19 +13636,19 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -13658,24 +13658,24 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>GPG3FS</t>
+          <t>GPG32A</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -13690,19 +13690,19 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG32A</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>GPG33D</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -13717,19 +13717,19 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33D</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>GPG33E</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -13744,19 +13744,19 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -13771,19 +13771,19 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -13793,24 +13793,24 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 17 mål, engelska: 2 mål (diff 15)</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>GPG3JD</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -13820,24 +13820,24 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -13852,19 +13852,19 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 18 mål, engelska: 2 mål (diff 16)</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -13874,24 +13874,24 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GPG3AB</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -13901,24 +13901,24 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (5 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AB</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>GPG3AF</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -13933,19 +13933,19 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>GPG3AF</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -13965,14 +13965,14 @@
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>GPG3BD</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -13987,19 +13987,19 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>GPG3BE</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -14009,24 +14009,24 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BE</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>PG3031</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -14041,19 +14041,19 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -14063,24 +14063,24 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -14090,24 +14090,24 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>PG3056</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -14117,24 +14117,24 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>PG3061</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -14149,19 +14149,19 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -14171,29 +14171,29 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -14203,51 +14203,51 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -14257,24 +14257,24 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -14284,24 +14284,24 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
+          <t>Svenska: 27 mål, engelska: 2 mål (diff 25)</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -14316,19 +14316,19 @@
       </c>
       <c r="E514" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GPG3CN</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -14338,186 +14338,186 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>GPG3FS</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -14527,24 +14527,24 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -14554,51 +14554,51 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>GPG3FU</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -14608,24 +14608,24 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 2 mål (diff 7)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -14635,24 +14635,24 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>GPG3JD</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -14662,51 +14662,51 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>GRK323</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -14721,19 +14721,19 @@
       </c>
       <c r="E529" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -14743,132 +14743,132 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>GRK32C</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>GRK32C</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>GRK36J</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>GRK36M</t>
+          <t>PG3031</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -14878,24 +14878,24 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>GRK36N</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -14905,51 +14905,51 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>GRK3B4</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>PG3056</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -14964,19 +14964,19 @@
       </c>
       <c r="E538" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>PG3061</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -14986,24 +14986,24 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E539" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -15013,24 +15013,24 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -15040,24 +15040,24 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>Svenska: 2 mål, engelska: 0 mål (diff 2)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E541" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -15067,24 +15067,24 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E542" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -15094,24 +15094,24 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E543" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>GRV2FC</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -15121,51 +15121,51 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
         </is>
       </c>
       <c r="E544" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E545" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -15175,24 +15175,24 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 2 mål (diff 3)</t>
+          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -15207,19 +15207,19 @@
       </c>
       <c r="E547" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -15229,78 +15229,78 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
         </is>
       </c>
       <c r="E548" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E549" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
         </is>
       </c>
       <c r="E550" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -15310,24 +15310,24 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E551" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -15337,24 +15337,24 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 4 mål (diff 1)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E552" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -15364,24 +15364,24 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E553" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>RV1046</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -15391,51 +15391,51 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E555" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -15445,51 +15445,51 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 9 mål, engelska: 2 mål (diff 7)</t>
         </is>
       </c>
       <c r="E556" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>RV1049</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E557" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -15499,51 +15499,51 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
         </is>
       </c>
       <c r="E558" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E559" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>RV1053</t>
+          <t>GRK323</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -15553,24 +15553,24 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -15580,51 +15580,51 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
         </is>
       </c>
       <c r="E561" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E562" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>RV1056</t>
+          <t>GRK32C</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -15634,51 +15634,51 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
       <c r="E563" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>RV1057</t>
+          <t>GRK32C</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E564" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>RV1058</t>
+          <t>GRK36J</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -15693,19 +15693,19 @@
       </c>
       <c r="E565" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36J</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>GRK36M</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -15715,24 +15715,24 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E566" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36M</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>GSK2PM</t>
+          <t>GRK36N</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -15742,24 +15742,24 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E567" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36N</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>GRK3B4</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -15774,19 +15774,19 @@
       </c>
       <c r="E568" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>GSK2PP</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -15801,19 +15801,19 @@
       </c>
       <c r="E569" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -15823,24 +15823,24 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E570" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -15850,24 +15850,24 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E571" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>GSK2PS</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -15877,24 +15877,24 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 2 mål, engelska: 0 mål (diff 2)</t>
         </is>
       </c>
       <c r="E572" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>GSK2PT</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -15904,24 +15904,24 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E573" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -15931,24 +15931,24 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E574" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>GSK2PV</t>
+          <t>GRV2FC</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -15958,24 +15958,24 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E575" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -15985,24 +15985,24 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E576" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -16012,51 +16012,51 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 5 mål, engelska: 2 mål (diff 3)</t>
         </is>
       </c>
       <c r="E577" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E578" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -16066,105 +16066,105 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E579" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E580" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E581" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E582" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -16174,51 +16174,51 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 3 mål, engelska: 4 mål (diff 1)</t>
         </is>
       </c>
       <c r="E583" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E584" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>RV1046</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -16228,24 +16228,24 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E585" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -16255,51 +16255,51 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 1 mål (diff 15)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E586" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E587" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>RV1049</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -16309,24 +16309,24 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E588" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -16336,51 +16336,51 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 1 mål (diff 18)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E589" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E590" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>RV1053</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -16390,51 +16390,51 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E591" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E592" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -16444,51 +16444,51 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E593" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>RV1056</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E594" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
         <is>
-          <t>GSO3D8</t>
+          <t>RV1057</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -16498,24 +16498,24 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E595" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO3D8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>RV1058</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -16525,24 +16525,24 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E596" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -16552,51 +16552,51 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E597" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>GSK2PM</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E598" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -16606,51 +16606,51 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E599" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>GSK2PP</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E600" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -16660,24 +16660,24 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E601" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -16687,51 +16687,51 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E602" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>GSK2PS</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E603" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>GTR3B6</t>
+          <t>GSK2PT</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -16746,73 +16746,73 @@
       </c>
       <c r="E604" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E605" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>GSK2PV</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E606" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -16822,51 +16822,51 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Svenska: 2 mål, engelska: 7 mål (diff 5)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E607" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E608" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -16876,125 +16876,962 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 6 mål (diff 1)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E609" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (6 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E610" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E611" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E612" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
         <is>
+          <t>SK1050</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>SK2015</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>SK2015</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>SKA</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>GSO2PL</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>GSO2UA</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Svenska: 16 mål, engelska: 1 mål (diff 15)</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>GSO2UA</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>GSO2UC</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XU</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Svenska: 19 mål, engelska: 1 mål (diff 18)</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XU</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XV</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>GSO2XV</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>GSO33U</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>GSO33U</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>GSO3D8</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO3D8</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>SO1006</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>SO1019</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>SO1019</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>SO1030</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>SO1030</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>SO1044</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>SOA</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>GTR2UM</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>GTR2UM</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>GTR3B6</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>TR1007</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (sv)</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>TR1007</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>TR1011</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Svenska: 2 mål, engelska: 7 mål (diff 5)</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>TR1011</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (sv)</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Lärandemål skrivet som löpande text (2 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>TR1018</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Svenska: 7 mål, engelska: 6 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>TR1018</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (6 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
           <t>TR2004</t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B643" t="inlineStr">
         <is>
           <t>TRU</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>TR2004</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
         <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr">
+      <c r="D644" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E613" s="2" t="inlineStr">
+      <c r="E644" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E613"/>
+  <autoFilter ref="A1:E644"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -18220,6 +19057,68 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E612" r:id="rId1222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A613" r:id="rId1223"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E613" r:id="rId1224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A614" r:id="rId1225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E614" r:id="rId1226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A615" r:id="rId1227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E615" r:id="rId1228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A616" r:id="rId1229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E616" r:id="rId1230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A617" r:id="rId1231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E617" r:id="rId1232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A618" r:id="rId1233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E618" r:id="rId1234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A619" r:id="rId1235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E619" r:id="rId1236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A620" r:id="rId1237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E620" r:id="rId1238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A621" r:id="rId1239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E621" r:id="rId1240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A622" r:id="rId1241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E622" r:id="rId1242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A623" r:id="rId1243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E623" r:id="rId1244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A624" r:id="rId1245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E624" r:id="rId1246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A625" r:id="rId1247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E625" r:id="rId1248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A626" r:id="rId1249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E626" r:id="rId1250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A627" r:id="rId1251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E627" r:id="rId1252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A628" r:id="rId1253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E628" r:id="rId1254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A629" r:id="rId1255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E629" r:id="rId1256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A630" r:id="rId1257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E630" r:id="rId1258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A631" r:id="rId1259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E631" r:id="rId1260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A632" r:id="rId1261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E632" r:id="rId1262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A633" r:id="rId1263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E633" r:id="rId1264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A634" r:id="rId1265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E634" r:id="rId1266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A635" r:id="rId1267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E635" r:id="rId1268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A636" r:id="rId1269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E636" r:id="rId1270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A637" r:id="rId1271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E637" r:id="rId1272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A638" r:id="rId1273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E638" r:id="rId1274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A639" r:id="rId1275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E639" r:id="rId1276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A640" r:id="rId1277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E640" r:id="rId1278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A641" r:id="rId1279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E641" r:id="rId1280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A642" r:id="rId1281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E642" r:id="rId1282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A643" r:id="rId1283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E643" r:id="rId1284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A644" r:id="rId1285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E644" r:id="rId1286"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$644</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$E$647</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E644"/>
+  <dimension ref="A1:E647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14674,7 +14674,7 @@
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>GPG3KA</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -14689,19 +14689,19 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KA</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>GPG3KB</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -14716,19 +14716,19 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KB</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>GPG3KB</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -14738,24 +14738,24 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KB</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -14770,19 +14770,19 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -14792,24 +14792,24 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -14824,19 +14824,19 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -14846,24 +14846,24 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>PG3031</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -14873,24 +14873,24 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -14910,14 +14910,14 @@
       </c>
       <c r="E536" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -14937,14 +14937,14 @@
       </c>
       <c r="E537" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>PG3056</t>
+          <t>PG3031</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -14964,14 +14964,14 @@
       </c>
       <c r="E538" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>PG3061</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -14986,19 +14986,19 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="E539" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -15008,29 +15008,29 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>PG3056</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -15040,24 +15040,24 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E541" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>PG3061</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -15067,24 +15067,24 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E542" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>PGA</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -15094,19 +15094,19 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E543" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -15121,19 +15121,19 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E544" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -15143,24 +15143,24 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E545" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -15175,19 +15175,19 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -15197,24 +15197,24 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
         </is>
       </c>
       <c r="E547" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -15224,24 +15224,24 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E548" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -15251,24 +15251,24 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
         </is>
       </c>
       <c r="E549" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -15278,24 +15278,24 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E550" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -15305,24 +15305,24 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
         </is>
       </c>
       <c r="E551" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -15332,24 +15332,24 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E552" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -15364,19 +15364,19 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
         </is>
       </c>
       <c r="E553" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -15386,24 +15386,24 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -15413,24 +15413,24 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E555" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -15445,19 +15445,19 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 2 mål (diff 7)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E556" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -15467,24 +15467,24 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
       <c r="E557" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -15494,24 +15494,24 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E558" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -15521,24 +15521,24 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 9 mål, engelska: 2 mål (diff 7)</t>
         </is>
       </c>
       <c r="E559" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>GRK323</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -15548,24 +15548,24 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -15580,19 +15580,19 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
+          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
         </is>
       </c>
       <c r="E561" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -15612,14 +15612,14 @@
       </c>
       <c r="E562" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>GRK32C</t>
+          <t>GRK323</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -15634,19 +15634,19 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E563" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>GRK32C</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -15656,24 +15656,24 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
         </is>
       </c>
       <c r="E564" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>GRK36J</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -15683,24 +15683,24 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E565" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>GRK36M</t>
+          <t>GRK32C</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -15715,19 +15715,19 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
       <c r="E566" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>GRK36N</t>
+          <t>GRK32C</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -15737,24 +15737,24 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E567" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>GRK3B4</t>
+          <t>GRK36J</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -15774,14 +15774,14 @@
       </c>
       <c r="E568" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36J</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>GRK36M</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -15796,19 +15796,19 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E569" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36M</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>GRK36N</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -15823,19 +15823,19 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E570" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36N</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>GRK3B4</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -15850,24 +15850,24 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E571" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -15877,24 +15877,24 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Svenska: 2 mål, engelska: 0 mål (diff 2)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E572" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -15904,24 +15904,24 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="E573" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -15936,14 +15936,14 @@
       </c>
       <c r="E574" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>GRV2FC</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -15958,19 +15958,19 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 2 mål, engelska: 0 mål (diff 2)</t>
         </is>
       </c>
       <c r="E575" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -15985,19 +15985,19 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E576" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -16012,19 +16012,19 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 2 mål (diff 3)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E577" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>GRV2FC</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -16034,24 +16034,24 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E578" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -16066,19 +16066,19 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E579" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -16093,19 +16093,19 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 2 mål (diff 3)</t>
         </is>
       </c>
       <c r="E580" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -16115,24 +16115,24 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E581" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -16142,24 +16142,24 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E582" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -16174,19 +16174,19 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 4 mål (diff 1)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E583" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -16196,24 +16196,24 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E584" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
         <is>
-          <t>RV1046</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -16223,24 +16223,24 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E585" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -16255,19 +16255,19 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 3 mål, engelska: 4 mål (diff 1)</t>
         </is>
       </c>
       <c r="E586" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -16287,14 +16287,14 @@
       </c>
       <c r="E587" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>RV1049</t>
+          <t>RV1046</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -16309,19 +16309,19 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="E588" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -16336,19 +16336,19 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="E589" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -16363,19 +16363,19 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E590" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
         <is>
-          <t>RV1053</t>
+          <t>RV1049</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -16395,14 +16395,14 @@
       </c>
       <c r="E591" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -16417,19 +16417,19 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E592" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -16449,14 +16449,14 @@
       </c>
       <c r="E593" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>RV1056</t>
+          <t>RV1053</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -16471,19 +16471,19 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E594" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
         <is>
-          <t>RV1057</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -16498,19 +16498,19 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E595" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>RV1058</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -16525,24 +16525,24 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E596" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>RV1056</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -16557,19 +16557,19 @@
       </c>
       <c r="E597" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>GSK2PM</t>
+          <t>RV1057</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -16579,24 +16579,24 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E598" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>RV1058</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -16611,14 +16611,14 @@
       </c>
       <c r="E599" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>GSK2PP</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -16633,19 +16633,19 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E600" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>GSK2PM</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -16660,19 +16660,19 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E601" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -16692,14 +16692,14 @@
       </c>
       <c r="E602" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
         <is>
-          <t>GSK2PS</t>
+          <t>GSK2PP</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -16714,19 +16714,19 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E603" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>GSK2PT</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -16746,14 +16746,14 @@
       </c>
       <c r="E604" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -16773,14 +16773,14 @@
       </c>
       <c r="E605" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>GSK2PV</t>
+          <t>GSK2PS</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -16795,19 +16795,19 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E606" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GSK2PT</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -16827,14 +16827,14 @@
       </c>
       <c r="E607" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -16849,19 +16849,19 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E608" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>GSK2PV</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -16876,19 +16876,19 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E609" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -16908,14 +16908,14 @@
       </c>
       <c r="E610" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -16925,24 +16925,24 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E611" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -16952,24 +16952,24 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E612" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -16984,19 +16984,19 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E613" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -17006,24 +17006,24 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E614" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -17043,19 +17043,19 @@
       </c>
       <c r="E615" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -17065,24 +17065,24 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="E616" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -17092,24 +17092,24 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 1 mål (diff 15)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="E617" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -17124,14 +17124,14 @@
       </c>
       <c r="E618" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -17146,19 +17146,19 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E619" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -17173,19 +17173,19 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 1 mål (diff 18)</t>
+          <t>Svenska: 16 mål, engelska: 1 mål (diff 15)</t>
         </is>
       </c>
       <c r="E620" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -17205,14 +17205,14 @@
       </c>
       <c r="E621" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>GSO2UC</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -17227,19 +17227,19 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E622" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -17249,24 +17249,24 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 19 mål, engelska: 1 mål (diff 18)</t>
         </is>
       </c>
       <c r="E623" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -17276,24 +17276,24 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E624" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -17303,24 +17303,24 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
         </is>
       </c>
       <c r="E625" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
         <is>
-          <t>GSO3D8</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -17330,24 +17330,24 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E626" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO3D8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -17362,19 +17362,19 @@
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
         </is>
       </c>
       <c r="E627" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -17384,24 +17384,24 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E628" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>GSO3D8</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -17411,24 +17411,24 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E629" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO3D8</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>SO1006</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -17443,19 +17443,19 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="E630" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -17465,24 +17465,24 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="E631" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -17492,29 +17492,29 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E632" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -17524,24 +17524,24 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
       <c r="E633" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -17556,19 +17556,19 @@
       </c>
       <c r="E634" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
         <is>
-          <t>GTR3B6</t>
+          <t>SO1044</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -17578,19 +17578,19 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="E635" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -17600,24 +17600,24 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="E636" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -17637,14 +17637,14 @@
       </c>
       <c r="E637" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>GTR3B6</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -17659,19 +17659,19 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>Svenska: 2 mål, engelska: 7 mål (diff 5)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="E638" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -17686,19 +17686,19 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E639" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -17708,24 +17708,24 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 6 mål (diff 1)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E640" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -17735,24 +17735,24 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (6 mål utan punktlista)</t>
+          <t>Svenska: 2 mål, engelska: 7 mål (diff 5)</t>
         </is>
       </c>
       <c r="E641" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -17762,24 +17762,24 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
+          <t>Lärandemål skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="E642" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
         <is>
-          <t>TR2004</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -17794,44 +17794,125 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+          <t>Svenska: 7 mål, engelska: 6 mål (diff 1)</t>
         </is>
       </c>
       <c r="E643" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
         <is>
+          <t>TR1018</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Saknar punktlista (en)</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Learning Outcomes skrivet som löpande text (6 mål utan punktlista)</t>
+        </is>
+      </c>
+      <c r="E644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>TR1028</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
+        </is>
+      </c>
+      <c r="E645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
           <t>TR2004</t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
+      <c r="B646" t="inlineStr">
         <is>
           <t>TRU</t>
         </is>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Paritetsskillnad</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
+        </is>
+      </c>
+      <c r="E646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>TR2004</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>TRU</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
         <is>
           <t>Saknar punktlista (en)</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr">
+      <c r="D647" t="inlineStr">
         <is>
           <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
-      <c r="E644" s="2" t="inlineStr">
+      <c r="E647" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E644"/>
+  <autoFilter ref="A1:E647"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -19119,6 +19200,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E643" r:id="rId1284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A644" r:id="rId1285"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E644" r:id="rId1286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A645" r:id="rId1287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E645" r:id="rId1288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A646" r:id="rId1289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E646" r:id="rId1290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A647" r:id="rId1291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E647" r:id="rId1292"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Samstämmighet svenska och engelska.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Samstämmighet svenska och engel" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$G$646</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Samstämmighet svenska och engel'!$A$1:$G$644</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G646"/>
+  <dimension ref="A1:G644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16475,7 +16475,7 @@
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2VW</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16485,7 +16485,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2022-03-15</t>
         </is>
       </c>
       <c r="D473" t="inlineStr"/>
@@ -16496,19 +16496,19 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>Svenska: 27 mål, engelska: 1 mål (diff 26)</t>
+          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
         </is>
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>GPG2SC</t>
+          <t>GPG2WR</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16518,30 +16518,30 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2021-12-03</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G474" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2SC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>GPG2VW</t>
+          <t>GPG2YG</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2022-03-15</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="D475" t="inlineStr"/>
@@ -16562,19 +16562,19 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 12 mål (diff 1)</t>
+          <t>Svenska: 8 mål, engelska: 3 mål (diff 5)</t>
         </is>
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2VW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>GPG2WR</t>
+          <t>GPG2YG</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16584,30 +16584,30 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2022-11-16</t>
         </is>
       </c>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (3 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G476" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2WR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>GPG2YG</t>
+          <t>GPG2YH</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="D477" t="inlineStr"/>
@@ -16628,19 +16628,19 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 3 mål (diff 5)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>GPG2YG</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16650,30 +16650,30 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2022-11-16</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (3 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>GPG2YH</t>
+          <t>GPG2Z3</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16683,30 +16683,30 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
+          <t>2022-12-12</t>
         </is>
       </c>
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2YH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>GPG2Z4</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16727,19 +16727,19 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z3</t>
+          <t>GPG2Z6</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16755,24 +16755,24 @@
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z4</t>
+          <t>GPG2Z7</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16793,19 +16793,19 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G482" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z6</t>
+          <t>GPG326</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="D483" t="inlineStr"/>
@@ -16826,19 +16826,19 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
         </is>
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>GPG2Z7</t>
+          <t>GPG326</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16848,30 +16848,30 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2023-01-24</t>
         </is>
       </c>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG2Z7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>GPG326</t>
+          <t>GPG327</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16892,19 +16892,19 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 1 mål (diff 7)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG327</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>GPG326</t>
+          <t>GPG328</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16920,24 +16920,24 @@
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG326</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>GPG327</t>
+          <t>GPG329</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -16963,14 +16963,14 @@
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG327</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>GPG328</t>
+          <t>GPG32A</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -16991,19 +16991,19 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
         </is>
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG328</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG32A</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>GPG329</t>
+          <t>GPG33D</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="D489" t="inlineStr"/>
@@ -17024,19 +17024,19 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG329</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33D</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>GPG32A</t>
+          <t>GPG33E</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="D490" t="inlineStr"/>
@@ -17057,19 +17057,19 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 0 mål (diff 9)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG32A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>GPG33D</t>
+          <t>GPG33F</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -17090,19 +17090,19 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>GPG33E</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -17112,7 +17112,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="D492" t="inlineStr"/>
@@ -17123,19 +17123,19 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 17 mål, engelska: 2 mål (diff 15)</t>
         </is>
       </c>
       <c r="G492" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>GPG33F</t>
+          <t>GPG36A</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -17145,30 +17145,30 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2023-02-27</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G493" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG33F</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -17189,19 +17189,19 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Svenska: 17 mål, engelska: 2 mål (diff 15)</t>
+          <t>Svenska: 18 mål, engelska: 2 mål (diff 16)</t>
         </is>
       </c>
       <c r="G494" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>GPG36A</t>
+          <t>GPG36B</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -17227,14 +17227,14 @@
       </c>
       <c r="G495" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG3AB</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17244,30 +17244,30 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>Svenska: 18 mål, engelska: 2 mål (diff 16)</t>
+          <t>Learning Outcomes skrivet som löpande text (5 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G496" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AB</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>GPG36B</t>
+          <t>GPG3AF</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17277,30 +17277,30 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="G497" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG36B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>GPG3AB</t>
+          <t>GPG3AF</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17321,19 +17321,19 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (5 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G498" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>GPG3AF</t>
+          <t>GPG3BD</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17343,7 +17343,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="D499" t="inlineStr"/>
@@ -17354,19 +17354,19 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G499" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>GPG3AF</t>
+          <t>GPG3BE</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17376,30 +17376,30 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BE</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>GPG3BD</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17409,7 +17409,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="D501" t="inlineStr"/>
@@ -17420,19 +17420,19 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
         </is>
       </c>
       <c r="G501" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>GPG3BE</t>
+          <t>GPG3CF</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17442,30 +17442,30 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G502" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3BE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17491,14 +17491,14 @@
       </c>
       <c r="G503" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>GPG3CF</t>
+          <t>GPG3CG</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17524,14 +17524,14 @@
       </c>
       <c r="G504" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17552,19 +17552,19 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
+          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
         </is>
       </c>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>GPG3CG</t>
+          <t>GPG3CH</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17590,14 +17590,14 @@
       </c>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17623,14 +17623,14 @@
       </c>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>GPG3CH</t>
+          <t>GPG3CJ</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17656,14 +17656,14 @@
       </c>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG3CK</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17684,19 +17684,19 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>GPG3CJ</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17712,24 +17712,24 @@
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 26 mål, engelska: 2 mål (diff 24)</t>
         </is>
       </c>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>GPG3CK</t>
+          <t>GPG3CL</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17745,24 +17745,24 @@
       <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G511" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG3CN</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17772,7 +17772,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="D512" t="inlineStr"/>
@@ -17783,19 +17783,19 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>Svenska: 27 mål, engelska: 2 mål (diff 25)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>GPG3CL</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17805,30 +17805,30 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
         </is>
       </c>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>GPG3CN</t>
+          <t>GPG3EU</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17838,30 +17838,30 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G514" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3CN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17882,19 +17882,19 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>Svenska: 15 mål, engelska: 2 mål (diff 13)</t>
+          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
         </is>
       </c>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>GPG3EU</t>
+          <t>GPG3EV</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17920,14 +17920,14 @@
       </c>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D517" t="inlineStr"/>
@@ -17948,19 +17948,19 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 2 mål (diff 11)</t>
+          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
         </is>
       </c>
       <c r="G517" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>GPG3EV</t>
+          <t>GPG3FR</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17970,30 +17970,30 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G518" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3EV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG3FS</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -18014,19 +18014,19 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>Svenska: 1 mål, engelska: 0 mål (diff 1)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G519" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>GPG3FR</t>
+          <t>GPG3FT</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -18042,24 +18042,24 @@
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G520" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>GPG3FS</t>
+          <t>GPG3FU</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -18080,19 +18080,19 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G521" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>GPG3FT</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -18113,19 +18113,19 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
         </is>
       </c>
       <c r="G522" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>GPG3FU</t>
+          <t>GPG3FV</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -18141,24 +18141,24 @@
       <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G523" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GPG3JD</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D524" t="inlineStr"/>
@@ -18179,19 +18179,19 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 1 mål (diff 4)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G524" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>GPG3FV</t>
+          <t>GPG3KA</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -18201,30 +18201,30 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D525" t="inlineStr"/>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G525" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3FV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KA</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>GPG3JD</t>
+          <t>GPG3KB</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -18234,7 +18234,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D526" t="inlineStr"/>
@@ -18245,19 +18245,19 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="G526" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3JD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KB</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>GPG3KA</t>
+          <t>GPG3KB</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -18273,24 +18273,24 @@
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G527" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KB</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>GPG3KB</t>
+          <t>PG2043</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -18300,10 +18300,14 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr"/>
+          <t>2012-10-09</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>2013-05-15</t>
+        </is>
+      </c>
       <c r="E528" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -18311,19 +18315,19 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G528" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>GPG3KB</t>
+          <t>PG2048</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -18333,30 +18337,34 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr"/>
+          <t>2013-03-15</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>2014-02-03</t>
+        </is>
+      </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G529" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPG3KB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>PG2043</t>
+          <t>PG3023</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -18366,12 +18374,12 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>2012-10-09</t>
+          <t>2013-03-15</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>2013-05-15</t>
+          <t>2014-02-03</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -18386,14 +18394,14 @@
       </c>
       <c r="G530" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>PG2048</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -18403,14 +18411,10 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>2013-03-15</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>2014-02-03</t>
-        </is>
-      </c>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -18418,19 +18422,19 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="G531" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG2048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>PG3023</t>
+          <t>PG3024</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -18440,34 +18444,30 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>2013-03-15</t>
-        </is>
-      </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>2014-02-03</t>
-        </is>
-      </c>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G532" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
+          <t>2013-07-03</t>
         </is>
       </c>
       <c r="D533" t="inlineStr"/>
@@ -18493,14 +18493,14 @@
       </c>
       <c r="G533" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>PG3024</t>
+          <t>PG3025</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
+          <t>2013-07-03</t>
         </is>
       </c>
       <c r="D534" t="inlineStr"/>
@@ -18526,14 +18526,14 @@
       </c>
       <c r="G534" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>PG3031</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -18543,10 +18543,14 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>2013-07-03</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr"/>
+          <t>2014-05-14</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>2017-11-22</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -18554,19 +18558,19 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G535" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>PG3025</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -18576,30 +18580,30 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>2013-07-03</t>
+          <t>2015-08-17</t>
         </is>
       </c>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="G536" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>PG3031</t>
+          <t>PG3041</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -18609,34 +18613,30 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>2014-05-14</t>
-        </is>
-      </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>2017-11-22</t>
-        </is>
-      </c>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G537" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3031</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>PG3056</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -18646,10 +18646,14 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>2015-08-17</t>
-        </is>
-      </c>
-      <c r="D538" t="inlineStr"/>
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2017-01-25</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -18657,19 +18661,19 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G538" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>PG3041</t>
+          <t>PG3061</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -18679,30 +18683,34 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>2015-08-17</t>
-        </is>
-      </c>
-      <c r="D539" t="inlineStr"/>
+          <t>2016-12-01</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2019-03-15</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G539" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3041</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>PG3056</t>
+          <t>PG3065</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -18712,14 +18720,10 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
-        </is>
-      </c>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>2017-01-25</t>
-        </is>
-      </c>
+          <t>2017-03-09</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -18727,36 +18731,32 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="G540" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>PG3061</t>
+          <t>ARK25B</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>2016-12-01</t>
-        </is>
-      </c>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>2019-03-15</t>
-        </is>
-      </c>
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -18764,29 +18764,29 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G541" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3061</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>PG3065</t>
+          <t>ARK25C</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>PGA</t>
+          <t>RKA</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>2017-03-09</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D542" t="inlineStr"/>
@@ -18797,19 +18797,19 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G542" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PG3065</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>ARK25B</t>
+          <t>GRK2EF</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D543" t="inlineStr"/>
@@ -18830,19 +18830,19 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G543" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>ARK25C</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="D544" t="inlineStr"/>
@@ -18863,19 +18863,19 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
         </is>
       </c>
       <c r="G544" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ARK25C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>GRK2EF</t>
+          <t>GRK2P3</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -18885,30 +18885,30 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2021-03-18</t>
         </is>
       </c>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G545" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2EF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -18929,19 +18929,19 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
+          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
         </is>
       </c>
       <c r="G546" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>GRK2P3</t>
+          <t>GRK2P4</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -18967,14 +18967,14 @@
       </c>
       <c r="G547" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="D548" t="inlineStr"/>
@@ -18995,19 +18995,19 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
+          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
         </is>
       </c>
       <c r="G548" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>GRK2P4</t>
+          <t>GRK2Q4</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -19017,7 +19017,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="D549" t="inlineStr"/>
@@ -19033,14 +19033,14 @@
       </c>
       <c r="G549" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2P4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -19061,19 +19061,19 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
+          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
         </is>
       </c>
       <c r="G550" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q4</t>
+          <t>GRK2Q5</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -19099,14 +19099,14 @@
       </c>
       <c r="G551" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>GRK2R7</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -19116,7 +19116,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D552" t="inlineStr"/>
@@ -19127,19 +19127,19 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>Svenska: 11 mål, engelska: 2 mål (diff 9)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="G552" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>GRK2Q5</t>
+          <t>GRK2R8</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -19149,30 +19149,30 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="G553" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2Q5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>GRK2R7</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="D554" t="inlineStr"/>
@@ -19193,19 +19193,19 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
       <c r="G554" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>GRK2R8</t>
+          <t>GRK2TW</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -19215,30 +19215,30 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="D555" t="inlineStr"/>
       <c r="E555" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G555" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2R8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -19248,7 +19248,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="D556" t="inlineStr"/>
@@ -19259,19 +19259,19 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Svenska: 9 mål, engelska: 2 mål (diff 7)</t>
         </is>
       </c>
       <c r="G556" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>GRK2TW</t>
+          <t>GRK2TY</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2022-02-04</t>
         </is>
       </c>
       <c r="D557" t="inlineStr"/>
@@ -19292,19 +19292,19 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G557" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -19325,19 +19325,19 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 2 mål (diff 7)</t>
+          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
         </is>
       </c>
       <c r="G558" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>GRK2TY</t>
+          <t>GRK2TZ</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -19363,14 +19363,14 @@
       </c>
       <c r="G559" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>GRK323</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="D560" t="inlineStr"/>
@@ -19391,19 +19391,19 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 2 mål (diff 8)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G560" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>GRK2TZ</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -19413,30 +19413,30 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="D561" t="inlineStr"/>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
         </is>
       </c>
       <c r="G561" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK2TZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>GRK323</t>
+          <t>GRK324</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -19452,24 +19452,24 @@
       <c r="D562" t="inlineStr"/>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G562" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK323</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GRK32C</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -19479,7 +19479,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="D563" t="inlineStr"/>
@@ -19490,19 +19490,19 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Svenska: 22 mål, engelska: 2 mål (diff 20)</t>
+          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
         </is>
       </c>
       <c r="G563" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>GRK324</t>
+          <t>GRK32C</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -19512,7 +19512,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="D564" t="inlineStr"/>
@@ -19523,19 +19523,19 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G564" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK324</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
         <is>
-          <t>GRK32C</t>
+          <t>GRK36J</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="D565" t="inlineStr"/>
@@ -19556,19 +19556,19 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 1 mål (diff 2)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G565" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36J</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>GRK32C</t>
+          <t>GRK36M</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -19578,30 +19578,30 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="D566" t="inlineStr"/>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="G566" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK32C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36M</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
         <is>
-          <t>GRK36J</t>
+          <t>GRK36N</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="D567" t="inlineStr"/>
@@ -19622,19 +19622,19 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="G567" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36N</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>GRK36M</t>
+          <t>GRK3B4</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="D568" t="inlineStr"/>
@@ -19655,19 +19655,19 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G568" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
         <is>
-          <t>GRK36N</t>
+          <t>GRK3CQ</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="D569" t="inlineStr"/>
@@ -19688,19 +19688,19 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G569" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK36N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
         <is>
-          <t>GRK3B4</t>
+          <t>RK1068</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -19710,10 +19710,14 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
-        </is>
-      </c>
-      <c r="D570" t="inlineStr"/>
+          <t>2016-09-13</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>2018-12-21</t>
+        </is>
+      </c>
       <c r="E570" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -19721,19 +19725,19 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
         </is>
       </c>
       <c r="G570" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3B4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
         <is>
-          <t>GRK3CQ</t>
+          <t>RK3043</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -19743,7 +19747,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2014-09-19</t>
         </is>
       </c>
       <c r="D571" t="inlineStr"/>
@@ -19754,36 +19758,32 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G571" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRK3CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
         <is>
-          <t>RK1068</t>
+          <t>GRV22R</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
-        </is>
-      </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>2018-12-21</t>
-        </is>
-      </c>
+          <t>2018-04-26</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -19791,29 +19791,29 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 0 mål (diff 7)</t>
+          <t>Svenska: 2 mål, engelska: 0 mål (diff 2)</t>
         </is>
       </c>
       <c r="G572" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK1068</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
         <is>
-          <t>RK3043</t>
+          <t>GRV266</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>RKA</t>
+          <t>RVA</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>2014-09-19</t>
+          <t>2019-02-21</t>
         </is>
       </c>
       <c r="D573" t="inlineStr"/>
@@ -19824,19 +19824,19 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G573" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RK3043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
         <is>
-          <t>GRV22R</t>
+          <t>GRV2CE</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -19846,7 +19846,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="D574" t="inlineStr"/>
@@ -19857,19 +19857,19 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>Svenska: 2 mål, engelska: 0 mål (diff 2)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G574" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV22R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
         <is>
-          <t>GRV266</t>
+          <t>GRV2FC</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>2019-02-21</t>
+          <t>2020-03-05</t>
         </is>
       </c>
       <c r="D575" t="inlineStr"/>
@@ -19895,14 +19895,14 @@
       </c>
       <c r="G575" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
         <is>
-          <t>GRV2CE</t>
+          <t>GRV2MK</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>2019-11-28</t>
+          <t>2021-02-18</t>
         </is>
       </c>
       <c r="D576" t="inlineStr"/>
@@ -19923,19 +19923,19 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G576" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
         <is>
-          <t>GRV2FC</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -19945,7 +19945,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="D577" t="inlineStr"/>
@@ -19956,19 +19956,19 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 5 mål, engelska: 2 mål (diff 3)</t>
         </is>
       </c>
       <c r="G577" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2FC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
         <is>
-          <t>GRV2MK</t>
+          <t>GRV3BF</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -19978,30 +19978,30 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>2021-02-18</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="D578" t="inlineStr"/>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G578" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV2MK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>RV1015</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2007-04-04</t>
         </is>
       </c>
       <c r="D579" t="inlineStr"/>
@@ -20022,19 +20022,19 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 2 mål (diff 3)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G579" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
         <is>
-          <t>GRV3BF</t>
+          <t>RV1034</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -20044,30 +20044,30 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="D580" t="inlineStr"/>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G580" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRV3BF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
         <is>
-          <t>RV1015</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -20077,30 +20077,30 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>2007-04-04</t>
+          <t>2009-05-13</t>
         </is>
       </c>
       <c r="D581" t="inlineStr"/>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G581" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
         <is>
-          <t>RV1034</t>
+          <t>RV1038</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -20110,30 +20110,30 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>2007-10-03</t>
+          <t>2009-05-13</t>
         </is>
       </c>
       <c r="D582" t="inlineStr"/>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G582" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1039</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -20143,30 +20143,30 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>2009-05-13</t>
+          <t>2009-06-08</t>
         </is>
       </c>
       <c r="D583" t="inlineStr"/>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 4 mål (diff 1)</t>
         </is>
       </c>
       <c r="G583" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
         <is>
-          <t>RV1038</t>
+          <t>RV1045</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -20176,30 +20176,30 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>2009-05-13</t>
+          <t>2013-05-23</t>
         </is>
       </c>
       <c r="D584" t="inlineStr"/>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G584" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
         <is>
-          <t>RV1039</t>
+          <t>RV1046</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>2009-06-08</t>
+          <t>2014-01-30</t>
         </is>
       </c>
       <c r="D585" t="inlineStr"/>
@@ -20220,19 +20220,19 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 4 mål (diff 1)</t>
+          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
         </is>
       </c>
       <c r="G585" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1039</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>RV1045</t>
+          <t>RV1047</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -20242,7 +20242,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>2013-05-23</t>
+          <t>2014-01-30</t>
         </is>
       </c>
       <c r="D586" t="inlineStr"/>
@@ -20253,19 +20253,19 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
         </is>
       </c>
       <c r="G586" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
         <is>
-          <t>RV1046</t>
+          <t>RV1048</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -20275,7 +20275,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>2014-01-30</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D587" t="inlineStr"/>
@@ -20286,19 +20286,19 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 0 mål (diff 8)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G587" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>RV1047</t>
+          <t>RV1049</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>2014-01-30</t>
+          <t>2014-11-21</t>
         </is>
       </c>
       <c r="D588" t="inlineStr"/>
@@ -20319,19 +20319,19 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>Svenska: 6 mål, engelska: 0 mål (diff 6)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G588" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
         <is>
-          <t>RV1048</t>
+          <t>RV1051</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2015-02-26</t>
         </is>
       </c>
       <c r="D589" t="inlineStr"/>
@@ -20357,14 +20357,14 @@
       </c>
       <c r="G589" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>RV1049</t>
+          <t>RV1052</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>2014-11-21</t>
+          <t>2015-02-26</t>
         </is>
       </c>
       <c r="D590" t="inlineStr"/>
@@ -20385,19 +20385,19 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G590" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
         <is>
-          <t>RV1051</t>
+          <t>RV1053</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -20423,14 +20423,14 @@
       </c>
       <c r="G591" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>RV1052</t>
+          <t>RV1054</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -20456,14 +20456,14 @@
       </c>
       <c r="G592" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
         <is>
-          <t>RV1053</t>
+          <t>RV1055</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -20473,7 +20473,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>2015-02-26</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D593" t="inlineStr"/>
@@ -20484,19 +20484,19 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G593" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>RV1054</t>
+          <t>RV1056</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>2015-02-26</t>
+          <t>2016-03-03</t>
         </is>
       </c>
       <c r="D594" t="inlineStr"/>
@@ -20522,14 +20522,14 @@
       </c>
       <c r="G594" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1054</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
         <is>
-          <t>RV1055</t>
+          <t>RV1057</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -20550,19 +20550,19 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G595" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1055</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>RV1056</t>
+          <t>RV1058</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -20583,29 +20583,29 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G596" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1056</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
         <is>
-          <t>RV1057</t>
+          <t>GSK2K2</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="D597" t="inlineStr"/>
@@ -20616,29 +20616,29 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G597" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1057</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>RV1058</t>
+          <t>GSK2PM</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RVA</t>
+          <t>SKA</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D598" t="inlineStr"/>
@@ -20649,19 +20649,19 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G598" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=RV1058</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
         <is>
-          <t>GSK2K2</t>
+          <t>GSK2PN</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -20671,7 +20671,7 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D599" t="inlineStr"/>
@@ -20682,19 +20682,19 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G599" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>GSK2PM</t>
+          <t>GSK2PP</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -20715,19 +20715,19 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G600" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" s="2" t="inlineStr">
         <is>
-          <t>GSK2PN</t>
+          <t>GSK2PQ</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -20748,19 +20748,19 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G601" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>GSK2PP</t>
+          <t>GSK2PR</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -20773,7 +20773,11 @@
           <t>2021-04-12</t>
         </is>
       </c>
-      <c r="D602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>2022-01-21</t>
+        </is>
+      </c>
       <c r="E602" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -20786,14 +20790,14 @@
       </c>
       <c r="G602" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" s="2" t="inlineStr">
         <is>
-          <t>GSK2PQ</t>
+          <t>GSK2PS</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -20814,19 +20818,19 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G603" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>GSK2PR</t>
+          <t>GSK2PT</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -20839,11 +20843,7 @@
           <t>2021-04-12</t>
         </is>
       </c>
-      <c r="D604" t="inlineStr">
-        <is>
-          <t>2022-01-21</t>
-        </is>
-      </c>
+      <c r="D604" t="inlineStr"/>
       <c r="E604" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -20851,19 +20851,19 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G604" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
         <is>
-          <t>GSK2PS</t>
+          <t>GSK2PU</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -20884,19 +20884,19 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G605" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>GSK2PT</t>
+          <t>GSK2PV</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -20922,14 +20922,14 @@
       </c>
       <c r="G606" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
         <is>
-          <t>GSK2PU</t>
+          <t>GSK2PW</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -20950,19 +20950,19 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G607" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>GSK2PV</t>
+          <t>GSK2QE</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="D608" t="inlineStr"/>
@@ -20983,19 +20983,19 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G608" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
         <is>
-          <t>GSK2PW</t>
+          <t>GSK2UH</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="D609" t="inlineStr"/>
@@ -21016,19 +21016,19 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G609" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2PW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>GSK2QE</t>
+          <t>GSK2UJ</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -21038,7 +21038,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>2021-05-31</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="D610" t="inlineStr"/>
@@ -21049,19 +21049,19 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G610" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2QE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" s="2" t="inlineStr">
         <is>
-          <t>GSK2UH</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -21071,30 +21071,34 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>2022-02-21</t>
-        </is>
-      </c>
-      <c r="D611" t="inlineStr"/>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>2015-08-24</t>
+        </is>
+      </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G611" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
         <is>
-          <t>GSK2UJ</t>
+          <t>SK1018</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -21104,30 +21108,34 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>2022-02-21</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr"/>
+          <t>2008-01-01</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>2015-08-24</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G612" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSK2UJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>SK1050</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -21137,34 +21145,34 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2011-04-19</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>2015-08-24</t>
+          <t>2016-06-28</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
         </is>
       </c>
       <c r="G613" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" s="2" t="inlineStr">
         <is>
-          <t>SK1018</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -21174,34 +21182,30 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
-        </is>
-      </c>
-      <c r="D614" t="inlineStr">
-        <is>
-          <t>2015-08-24</t>
-        </is>
-      </c>
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr"/>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="G614" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
         <is>
-          <t>SK1050</t>
+          <t>SK2015</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -21211,44 +21215,40 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>2011-04-19</t>
-        </is>
-      </c>
-      <c r="D615" t="inlineStr">
-        <is>
-          <t>2016-06-28</t>
-        </is>
-      </c>
+          <t>2015-09-17</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr"/>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 0 mål (diff 4)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G615" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>GSO2PL</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>2015-09-17</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="D616" t="inlineStr"/>
@@ -21259,52 +21259,52 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="G616" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" s="2" t="inlineStr">
         <is>
-          <t>SK2015</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>SKA</t>
+          <t>SOA</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>2015-09-17</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="D617" t="inlineStr"/>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 16 mål, engelska: 1 mål (diff 15)</t>
         </is>
       </c>
       <c r="G617" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SK2015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
         <is>
-          <t>GSO2PL</t>
+          <t>GSO2UA</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -21314,30 +21314,30 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2022-02-07</t>
         </is>
       </c>
       <c r="D618" t="inlineStr"/>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G618" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2PL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>GSO2UC</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -21358,19 +21358,19 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Svenska: 16 mål, engelska: 1 mål (diff 15)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G619" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
         </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
         <is>
-          <t>GSO2UA</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -21380,30 +21380,30 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="D620" t="inlineStr"/>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 19 mål, engelska: 1 mål (diff 18)</t>
         </is>
       </c>
       <c r="G620" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
         <is>
-          <t>GSO2UC</t>
+          <t>GSO2XU</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -21413,30 +21413,30 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="D621" t="inlineStr"/>
       <c r="E621" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G621" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2UC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -21457,19 +21457,19 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>Svenska: 19 mål, engelska: 1 mål (diff 18)</t>
+          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
         </is>
       </c>
       <c r="G622" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
         <is>
-          <t>GSO2XU</t>
+          <t>GSO2XV</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -21495,14 +21495,14 @@
       </c>
       <c r="G623" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="D624" t="inlineStr"/>
@@ -21528,14 +21528,14 @@
       </c>
       <c r="G624" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
         <is>
-          <t>GSO2XV</t>
+          <t>GSO33U</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -21545,7 +21545,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2023-03-13</t>
         </is>
       </c>
       <c r="D625" t="inlineStr"/>
@@ -21561,14 +21561,14 @@
       </c>
       <c r="G625" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO2XV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>GSO3D8</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="D626" t="inlineStr"/>
@@ -21589,19 +21589,19 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Svenska: 13 mål, engelska: 1 mål (diff 12)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G626" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO3D8</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
         <is>
-          <t>GSO33U</t>
+          <t>SO1006</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -21611,30 +21611,30 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>2023-03-13</t>
+          <t>2007-01-09</t>
         </is>
       </c>
       <c r="D627" t="inlineStr"/>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
         </is>
       </c>
       <c r="G627" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO33U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
         <is>
-          <t>GSO3D8</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -21644,10 +21644,14 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="D628" t="inlineStr"/>
+          <t>2010-10-19</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
       <c r="E628" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -21655,19 +21659,19 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
         </is>
       </c>
       <c r="G628" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSO3D8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
         <is>
-          <t>SO1006</t>
+          <t>SO1019</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -21677,30 +21681,34 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>2007-01-09</t>
-        </is>
-      </c>
-      <c r="D629" t="inlineStr"/>
+          <t>2010-10-19</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>Svenska: 3 mål, engelska: 0 mål (diff 3)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G629" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
         </is>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -21710,12 +21718,12 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>2010-10-19</t>
+          <t>2013-03-14</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2013-08-19</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
@@ -21725,19 +21733,19 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>Svenska: 4 mål, engelska: 1 mål (diff 3)</t>
+          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
         </is>
       </c>
       <c r="G630" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
         <is>
-          <t>SO1019</t>
+          <t>SO1030</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -21747,12 +21755,12 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>2010-10-19</t>
+          <t>2013-03-14</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2013-08-19</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -21767,14 +21775,14 @@
       </c>
       <c r="G631" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1019</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>SO1044</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -21784,14 +21792,10 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>2013-03-14</t>
-        </is>
-      </c>
-      <c r="D632" t="inlineStr">
-        <is>
-          <t>2013-08-19</t>
-        </is>
-      </c>
+          <t>2017-03-13</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr"/>
       <c r="E632" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -21799,89 +21803,85 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Svenska: 9 mål, engelska: 1 mål (diff 8)</t>
+          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
         </is>
       </c>
       <c r="G632" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" s="2" t="inlineStr">
         <is>
-          <t>SO1030</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>2013-03-14</t>
-        </is>
-      </c>
-      <c r="D633" t="inlineStr">
-        <is>
-          <t>2013-08-19</t>
-        </is>
-      </c>
+          <t>2022-02-24</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr"/>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
         </is>
       </c>
       <c r="G633" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
         <is>
-          <t>SO1044</t>
+          <t>GTR2UM</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>SOA</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>2017-03-13</t>
+          <t>2022-02-24</t>
         </is>
       </c>
       <c r="D634" t="inlineStr"/>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>Svenska: 10 mål, engelska: 0 mål (diff 10)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G634" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SO1044</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>GTR3B6</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -21891,7 +21891,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="D635" t="inlineStr"/>
@@ -21902,19 +21902,19 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 1 mål (diff 6)</t>
+          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
         </is>
       </c>
       <c r="G635" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" s="2" t="inlineStr">
         <is>
-          <t>GTR2UM</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -21924,30 +21924,34 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
-        </is>
-      </c>
-      <c r="D636" t="inlineStr"/>
+          <t>2008-01-22</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>2009-08-26</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G636" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR2UM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" s="2" t="inlineStr">
         <is>
-          <t>GTR3B6</t>
+          <t>TR1007</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -21957,30 +21961,34 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
-        </is>
-      </c>
-      <c r="D637" t="inlineStr"/>
+          <t>2008-01-22</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>2009-08-26</t>
+        </is>
+      </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>Svenska: 5 mål, engelska: 0 mål (diff 5)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G637" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTR3B6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -21990,34 +21998,34 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>2008-01-22</t>
+          <t>2009-09-02</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>2009-08-26</t>
+          <t>2012-03-27</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Svenska: 2 mål, engelska: 7 mål (diff 5)</t>
         </is>
       </c>
       <c r="G638" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" s="2" t="inlineStr">
         <is>
-          <t>TR1007</t>
+          <t>TR1011</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -22027,34 +22035,34 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>2008-01-22</t>
+          <t>2009-09-02</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>2009-08-26</t>
+          <t>2012-03-27</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Saknar punktlista (sv)</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
+          <t>Lärandemål skrivet som löpande text (2 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G639" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -22064,12 +22072,12 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>2009-09-02</t>
+          <t>2014-02-20</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>2012-03-27</t>
+          <t>2015-01-28</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -22079,19 +22087,19 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>Svenska: 2 mål, engelska: 7 mål (diff 5)</t>
+          <t>Svenska: 7 mål, engelska: 6 mål (diff 1)</t>
         </is>
       </c>
       <c r="G640" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
         <is>
-          <t>TR1011</t>
+          <t>TR1018</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -22101,34 +22109,34 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>2009-09-02</t>
+          <t>2014-02-20</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>2012-03-27</t>
+          <t>2015-01-28</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Saknar punktlista (sv)</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Lärandemål skrivet som löpande text (2 mål utan punktlista)</t>
+          <t>Learning Outcomes skrivet som löpande text (6 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G641" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
         </is>
       </c>
     </row>
     <row r="642">
       <c r="A642" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>TR1028</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -22138,14 +22146,10 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>2014-02-20</t>
-        </is>
-      </c>
-      <c r="D642" t="inlineStr">
-        <is>
-          <t>2015-01-28</t>
-        </is>
-      </c>
+          <t>2015-12-07</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr"/>
       <c r="E642" t="inlineStr">
         <is>
           <t>Paritetsskillnad</t>
@@ -22153,19 +22157,19 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>Svenska: 7 mål, engelska: 6 mål (diff 1)</t>
+          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
         </is>
       </c>
       <c r="G642" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
         </is>
       </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
         <is>
-          <t>TR1018</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -22175,34 +22179,30 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>2014-02-20</t>
-        </is>
-      </c>
-      <c r="D643" t="inlineStr">
-        <is>
-          <t>2015-01-28</t>
-        </is>
-      </c>
+          <t>2014-01-30</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr"/>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Saknar punktlista (en)</t>
+          <t>Paritetsskillnad</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>Learning Outcomes skrivet som löpande text (6 mål utan punktlista)</t>
+          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
         </is>
       </c>
       <c r="G643" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1018</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
         <is>
-          <t>TR1028</t>
+          <t>TR2004</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -22212,94 +22212,28 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>2015-12-07</t>
+          <t>2014-01-30</t>
         </is>
       </c>
       <c r="D644" t="inlineStr"/>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Paritetsskillnad</t>
+          <t>Saknar punktlista (en)</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Svenska: 8 mål, engelska: 9 mål (diff 1)</t>
+          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
         </is>
       </c>
       <c r="G644" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" s="2" t="inlineStr">
-        <is>
-          <t>TR2004</t>
-        </is>
-      </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>2014-01-30</t>
-        </is>
-      </c>
-      <c r="D645" t="inlineStr"/>
-      <c r="E645" t="inlineStr">
-        <is>
-          <t>Paritetsskillnad</t>
-        </is>
-      </c>
-      <c r="F645" t="inlineStr">
-        <is>
-          <t>Svenska: 15 mål, engelska: 1 mål (diff 14)</t>
-        </is>
-      </c>
-      <c r="G645" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" s="2" t="inlineStr">
-        <is>
-          <t>TR2004</t>
-        </is>
-      </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>TRU</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>2014-01-30</t>
-        </is>
-      </c>
-      <c r="D646" t="inlineStr"/>
-      <c r="E646" t="inlineStr">
-        <is>
-          <t>Saknar punktlista (en)</t>
-        </is>
-      </c>
-      <c r="F646" t="inlineStr">
-        <is>
-          <t>Learning Outcomes skrivet som löpande text (1 mål utan punktlista)</t>
-        </is>
-      </c>
-      <c r="G646" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TR2004</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G646"/>
+  <autoFilter ref="A1:G644"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -23587,10 +23521,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G643" r:id="rId1284"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A644" r:id="rId1285"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G644" r:id="rId1286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A645" r:id="rId1287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G645" r:id="rId1288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A646" r:id="rId1289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G646" r:id="rId1290"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
